--- a/assets/constructions/examples/ctd_bs_cart_head.xlsx
+++ b/assets/constructions/examples/ctd_bs_cart_head.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,34 +559,56 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MKT2-90T16-L</t>
+          <t>R148C-12-0902</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>SANDVIK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fine boring unit</t>
+        </is>
+      </c>
       <c r="D2" t="n">
-        <v>10.3</v>
+        <v>6.3</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>68.40000000000001</v>
+        <v>36.5</v>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>62.7</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>32</v>
+        <v>18.3</v>
       </c>
       <c r="J2" t="n">
         <v>90</v>
@@ -597,28 +619,28 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>COR_CFB2:46</t>
+          <t>CFB_03_COR:NO2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>ISO_TC16T3H</t>
+          <t>ISO_TC0902H</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>TC16T3H</t>
+          <t>SAND_TC0902_H</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ISO</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -628,24 +650,30 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.21</v>
+        <v>0.161</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MKT1-90T09-R</t>
+          <t>MKT1-90T11-R</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -655,20 +683,20 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>32.5</v>
+        <v>42</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>33.7</v>
+        <v>45.3</v>
       </c>
       <c r="I3" t="n">
-        <v>19.1</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
         <v>90</v>
@@ -684,18 +712,18 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>COR_CFB2:25</t>
+          <t>COR_CFB2:30</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ISO_TC0902H</t>
+          <t>ISO_TC1102H</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>TC0902H</t>
+          <t>TC1102H</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -713,7 +741,7 @@
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -722,37 +750,49 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>419.81</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>34413.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R148C-33-1102</t>
+          <t>MKT2-90C06-R</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fine boring unit</t>
-        </is>
-      </c>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>24.1</v>
+      </c>
       <c r="I4" t="n">
-        <v>23</v>
+        <v>13.3</v>
       </c>
       <c r="J4" t="n">
         <v>90</v>
@@ -763,55 +803,69 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CFB_03_COR:NO3</t>
+          <t>COR_CFB2:19</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ISO_TC1102H</t>
+          <t>ISO_CC0602H</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>SAND_TC1102_H</t>
+          <t>CC0602H</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>ISO</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.307</v>
+        <v>0.03</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
+          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>30217.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MKT2-90T11-L</t>
+          <t>MKT2-90T09-R</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -821,20 +875,20 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>48.5</v>
+        <v>36.5</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>44.3</v>
+        <v>32.9</v>
       </c>
       <c r="I5" t="n">
-        <v>22.1</v>
+        <v>18.3</v>
       </c>
       <c r="J5" t="n">
         <v>90</v>
@@ -850,18 +904,18 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>COR_CFB2:30</t>
+          <t>COR_CFB2:25</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ISO_TC1102H</t>
+          <t>ISO_TC0902H</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>TC1102H</t>
+          <t>TC0902H</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -879,7 +933,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -888,12 +942,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>30217.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MKT1-90C06-R</t>
+          <t>MKT1-90T06-L</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -901,59 +969,49 @@
           <t>DEREK</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MKT</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>25.5</v>
+        <v>24.8</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>25.15</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
         <v>14.3</v>
       </c>
       <c r="J6" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.01</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CFB_03_COR:19</t>
+          <t>COR_CFB2:19</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ISO_CC0602H</t>
+          <t>ISO_TB0601H</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CC0602H</t>
+          <t>TB0601H</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -964,7 +1022,7 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -978,8 +1036,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2016 / DEREK Catalog RU</t>
-        </is>
+          <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>30217.22</v>
       </c>
     </row>
   </sheetData>
